--- a/DATA/random_normal_forecast_data.xlsx
+++ b/DATA/random_normal_forecast_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5e6b18ad1acc1266/Desktop/Vaccine_Tender/DATA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="102" documentId="8_{4AC4CF64-28C5-4046-81FC-BB8B210E8F65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2CD76CA2-5093-42A9-8B50-E2336C077B32}"/>
+  <xr:revisionPtr revIDLastSave="111" documentId="8_{4AC4CF64-28C5-4046-81FC-BB8B210E8F65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{159E750F-3F98-4CCC-947A-24603676EB46}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{A5115543-AC87-4E62-8A65-1522949D5C3B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="8" activeTab="9" xr2:uid="{A5115543-AC87-4E62-8A65-1522949D5C3B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet4" sheetId="4" r:id="rId1"/>
@@ -163,8 +163,8776 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet5!$A$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Measles</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Sheet5!$B$1:$K$1</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet5!$B$2:$K$2</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>310958942.10050154</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>398307195.85585243</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>529259051.05312687</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>808489575.54863513</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>856043755.18987906</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>409176288.14370888</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>637166647.06255186</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>818539166.74024522</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1284779014.732378</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>298623871.27539968</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-B82C-4E73-BE20-DE21B9202B65}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet5!$A$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Mumps</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Sheet5!$B$1:$K$1</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet5!$B$3:$K$3</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>34361328.72417558</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>47723828.221244819</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>53989180.429289483</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>35544351.285148725</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>47052936.830931753</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>57469492.299068414</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>58063252.076469153</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>54696339.296729423</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>74494287.881504849</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>97015119.122815117</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-B82C-4E73-BE20-DE21B9202B65}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet5!$A$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Rubella</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Sheet5!$B$1:$K$1</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet5!$B$4:$K$4</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>415261311.00445628</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>589518967.45621312</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>734748895.59781075</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>263396278.03989375</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>152681665.68067652</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>215164992.62842834</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>418752009.1447798</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>439751497.64303374</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1012076750.0298505</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>569433026.96055877</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-B82C-4E73-BE20-DE21B9202B65}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet5!$A$5</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Diphtheria</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Sheet5!$B$1:$K$1</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet5!$B$5:$K$5</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>776996995.74679041</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>688473259.88497734</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>472845159.87652242</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1223877877.9551761</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1251017714.384634</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1423919925.8317096</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1479669464.7233796</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1229309519.6429892</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1707500205.9181166</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1814436572.9055295</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-B82C-4E73-BE20-DE21B9202B65}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="4"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet5!$A$6</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Tetanus</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent5"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Sheet5!$B$1:$K$1</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet5!$B$6:$K$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>579644922.2105763</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>546556435.55415082</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>694154267.74801433</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>820877109.62421489</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>622090471.47168231</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>669538816.33656549</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>625356226.5192368</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>731721615.18468475</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>776525714.82073426</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>886654944.76104963</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000004-B82C-4E73-BE20-DE21B9202B65}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="5"/>
+          <c:order val="5"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet5!$A$7</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Pertussis</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent6"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Sheet5!$B$1:$K$1</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet5!$B$7:$K$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>313184875.6168254</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>339157945.94108933</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>306338534.75382996</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>311906186.00446719</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>423435182.11955917</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>292298059.83526272</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>436303363.073232</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>334186941.02066076</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>319156333.53295237</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>421023362.54656082</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000005-B82C-4E73-BE20-DE21B9202B65}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="6"/>
+          <c:order val="6"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet5!$A$8</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Hepatitis_B</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Sheet5!$B$1:$K$1</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet5!$B$8:$K$8</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>449867903.82097661</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>369543822.9680562</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>284057518.52427888</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>297659953.16591609</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>279271529.99433786</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>456005640.42371196</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>531633898.06096399</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>486226062.31165284</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>451425703.2068001</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>635156208.17945361</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000006-B82C-4E73-BE20-DE21B9202B65}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="7"/>
+          <c:order val="7"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet5!$A$9</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Hib</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Sheet5!$B$1:$K$1</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet5!$B$9:$K$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>294472329.1953209</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>348303936.39789993</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>296503033.56485379</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>263070934.2555798</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>275298506.05489188</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>404505448.73813003</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>334441618.6380294</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>342566304.42494577</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>391457855.54271138</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>479970556.01924264</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000007-B82C-4E73-BE20-DE21B9202B65}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="8"/>
+          <c:order val="8"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet5!$A$10</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Polio</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Sheet5!$B$1:$K$1</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet5!$B$10:$K$10</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>600004129.53646541</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>649527190.26470888</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>554923892.95376658</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>574295757.86416745</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>978767909.04237306</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>782806620.08718979</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>923680066.5083946</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>780787928.59745073</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1035908822.9655941</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1071934938.5922539</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000008-B82C-4E73-BE20-DE21B9202B65}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="9"/>
+          <c:order val="9"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet5!$A$11</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>HPV</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Sheet5!$B$1:$K$1</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet5!$B$11:$K$11</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>25915770.51731832</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>32672389.333723851</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>46720358.840827107</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>49694653.082315072</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>49016915.848422892</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>53464242.801456355</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>74005715.817854047</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>71176416.456565768</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>67407974.396937698</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>83965270.015881896</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000009-B82C-4E73-BE20-DE21B9202B65}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="10"/>
+          <c:order val="10"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet5!$A$12</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Rotavirus</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent5">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Sheet5!$B$1:$K$1</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet5!$B$12:$K$12</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>151905241.58038071</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>288904036.91733217</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>321108727.54186213</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>433995075.38211548</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>205226968.08876684</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>324913640.12742454</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>414649090.05854881</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>449248383.11757588</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>523615446.11135596</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>705580758.51733863</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{0000000A-B82C-4E73-BE20-DE21B9202B65}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="11"/>
+          <c:order val="11"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet5!$A$13</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>PCV</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent6">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Sheet5!$B$1:$K$1</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet5!$B$13:$K$13</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>236882000.24169743</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>303936532.15251517</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>309216079.21334451</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>350511157.83793527</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>364668081.30266196</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>441846031.4073289</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>388959990.46478218</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>271326248.2794922</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>488519472.43370849</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>420532429.29658371</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{0000000B-B82C-4E73-BE20-DE21B9202B65}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="1360580719"/>
+        <c:axId val="1360572559"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="1360580719"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1360572559"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1360572559"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1360580719"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet15!$A$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Measles</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Sheet15!$B$1:$K$1</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet15!$B$2:$K$2</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>247261081.24249551</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>544531067.98469281</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>605180319.35950935</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>758934576.69560158</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>556065848.22168982</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>882573464.88517976</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>98792333.830466211</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>419990010.70389265</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>872849240.09803843</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>754199547.04882061</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-1D11-4AB4-8A17-D738E316858C}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet15!$A$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Mumps</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Sheet15!$B$1:$K$1</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet15!$B$3:$K$3</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>39449727.696229212</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>41247541.05652982</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>55569811.119592145</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>43741954.100588419</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>25686487.989866488</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>15497984.909292381</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>42214897.944511309</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>59545589.636253566</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>74861195.414903581</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>62046248.428248778</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-1D11-4AB4-8A17-D738E316858C}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet15!$A$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Rubella</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Sheet15!$B$1:$K$1</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet15!$B$4:$K$4</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>312931607.86192805</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>261736917.85877714</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>356207545.02332509</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>687696142.15014565</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>577912984.87174463</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>999238534.95474911</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>570550129.2949512</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1013260406.3329521</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>708497787.06365919</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>917049450.4767983</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-1D11-4AB4-8A17-D738E316858C}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet15!$A$5</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Diphtheria</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Sheet15!$B$1:$K$1</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet15!$B$5:$K$5</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>777076702.64843607</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>508228721.08986032</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>515701901.19969463</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>766518980.45625961</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>981196372.78699028</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>888942906.5120163</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1265540530.7244077</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1187899013.9133747</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1471847613.6348763</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1661879606.7953668</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-1D11-4AB4-8A17-D738E316858C}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="4"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet15!$A$6</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Tetanus</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent5"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Sheet15!$B$1:$K$1</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet15!$B$6:$K$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>712021988.8411392</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>594746754.91864622</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>704903128.61953044</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>570301905.80458033</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>633324674.45372903</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>721484576.53231502</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>669870705.74944675</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>594780867.59579849</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>762908169.91673446</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>744874126.03588116</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000004-1D11-4AB4-8A17-D738E316858C}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="5"/>
+          <c:order val="5"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet15!$A$7</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Pertussis</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent6"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Sheet15!$B$1:$K$1</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet15!$B$7:$K$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>313184875.6168254</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>297220409.07591468</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>294334087.4388451</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>279473195.64215022</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>372227948.95388764</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>409148808.35050666</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>482987802.13550627</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>499039249.86834961</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>301671336.62628329</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>369518493.88666403</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000005-1D11-4AB4-8A17-D738E316858C}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="6"/>
+          <c:order val="6"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet15!$A$8</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Hepatitis_B</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Sheet15!$B$1:$K$1</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet15!$B$8:$K$8</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>449867903.82097661</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>403501764.67888731</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>468047938.47390473</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>471060330.80718112</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>587727846.39041424</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>368484775.35057414</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>352033274.8481006</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>417433808.69463336</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>611742495.22378755</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>552160612.86646414</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000006-1D11-4AB4-8A17-D738E316858C}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="7"/>
+          <c:order val="7"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet15!$A$9</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Hib</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Sheet15!$B$1:$K$1</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet15!$B$9:$K$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>335380421.76351452</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>303291277.34733528</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>308384151.61671501</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>288310877.71647352</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>339185317.71579212</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>439745710.42781752</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>308602703.72029364</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>376818307.78252274</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>394557015.19658792</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>433495351.63250607</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000007-1D11-4AB4-8A17-D738E316858C}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="8"/>
+          <c:order val="8"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet15!$A$10</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Polio</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Sheet15!$B$1:$K$1</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet15!$B$10:$K$10</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>716469135.2208643</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>743569499.8809123</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>525451510.27095741</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>836096165.87218428</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>530951394.04994923</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>738534178.00839627</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1003481680.3400334</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>841405973.43106174</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>830609216.24011087</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>964693065.10574746</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000008-1D11-4AB4-8A17-D738E316858C}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="9"/>
+          <c:order val="9"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet15!$A$11</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>HPV</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Sheet15!$B$1:$K$1</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet15!$B$11:$K$11</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>25915770.51731832</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>38743044.276719272</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>45723415.111616217</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>50295423.553656742</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>48080412.230381623</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>56509033.458049648</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>77364384.640003011</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>71558554.613944352</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>73411612.944510505</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>94459200.869543225</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000009-1D11-4AB4-8A17-D738E316858C}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="10"/>
+          <c:order val="10"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet15!$A$12</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Rotavirus</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent5">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Sheet15!$B$1:$K$1</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet15!$B$12:$K$12</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>192528423.28232914</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>288904036.91733217</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>370114448.41798627</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>448692699.81600904</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>260121669.98839098</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>301913888.98440117</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>743814124.29390776</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>585182007.17453361</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>724136716.86365819</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>702631628.27536368</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{0000000A-1D11-4AB4-8A17-D738E316858C}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="11"/>
+          <c:order val="11"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet15!$A$13</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>PCV</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent6">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Sheet15!$B$1:$K$1</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet15!$B$13:$K$13</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>252940083.3603006</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>303936532.15251517</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>317552763.67582494</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>386655651.47809207</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>308289669.11686397</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>351618050.87353635</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>149234087.09448025</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>442401613.81848264</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>537900172.23115742</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>284506084.92702264</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{0000000B-1D11-4AB4-8A17-D738E316858C}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="1755576192"/>
+        <c:axId val="1755579552"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="1755576192"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1755579552"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1755579552"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1755576192"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet20!$A$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Measles</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Sheet20!$B$1:$K$1</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet20!$B$2:$K$2</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>389300451.40042073</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>427554978.95093626</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>512762394.16087282</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1042625820.562032</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>889914300.58781743</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>957408119.96773267</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>774013415.70998394</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>983462176.50809884</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>863310254.97483563</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1585975420.6627636</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-1349-4D21-80D7-E23EAC793ED9}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet20!$A$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Mumps</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Sheet20!$B$1:$K$1</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet20!$B$3:$K$3</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>15606210.17351607</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>32224950.56138584</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>41431709.107195452</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>15437048.69029057</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>63245308.317527808</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>61811384.314757079</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>77837446.191440225</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>39092938.188328467</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>48227486.572642729</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>23625552.118376799</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-1349-4D21-80D7-E23EAC793ED9}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet20!$A$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Rubella</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Sheet20!$B$1:$K$1</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet20!$B$4:$K$4</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>190948844.07116279</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>515612384.54859674</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>401724375.25413734</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>833845846.65265334</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>448607495.71358192</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>493637466.77024353</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>615367495.07489061</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1250573329.867188</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1142557611.9038699</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>891572747.8911227</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-1349-4D21-80D7-E23EAC793ED9}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet20!$A$5</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Diphtheria</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Sheet20!$B$1:$K$1</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet20!$B$5:$K$5</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>777076702.64843607</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>813664216.8496089</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>711375545.55717063</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>717100875.50454879</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1026029996.5617836</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>818912301.43208647</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1677671894.6356816</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1320851358.2226534</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2227991034.3853669</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1582192927.283531</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-1349-4D21-80D7-E23EAC793ED9}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="4"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet20!$A$6</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Tetanus</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent5"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Sheet20!$B$1:$K$1</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet20!$B$6:$K$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>680320872.29568553</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>695081759.07180643</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>528200806.70503402</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>750404281.41329324</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>642091228.99453747</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>883894056.16960812</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>669211201.25162601</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>651638264.33043861</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>768579897.73030877</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>669864541.22796428</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000004-1349-4D21-80D7-E23EAC793ED9}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="5"/>
+          <c:order val="5"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet20!$A$7</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Pertussis</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent6"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Sheet20!$B$1:$K$1</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet20!$B$7:$K$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>313184875.6168254</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>297220409.07591468</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>437276119.25633711</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>313880182.47258073</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>391045314.5834775</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>391369034.27698696</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>462057889.49429256</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>373443696.16450548</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>367184315.96347958</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>330945258.38872534</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000005-1349-4D21-80D7-E23EAC793ED9}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="6"/>
+          <c:order val="6"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet20!$A$8</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Hepatitis_B</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Sheet20!$B$1:$K$1</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet20!$B$8:$K$8</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>313064095.43054122</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>494109545.4175849</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>551227913.124102</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>449895294.1011073</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>419113369.55403847</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>200875543.96746871</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>199435538.83370849</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>434920380.67531407</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>273620507.08289146</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>250999172.24124366</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000006-1349-4D21-80D7-E23EAC793ED9}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="7"/>
+          <c:order val="7"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet20!$A$9</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Hib</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Sheet20!$B$1:$K$1</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet20!$B$9:$K$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>301676114.75612402</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>268413511.17077488</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>316787427.73102039</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>318977411.89104074</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>404023708.82587326</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>320470435.97316575</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>333972916.70491564</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>420089367.56089514</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>384496250.64168549</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>402406723.8234179</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000007-1349-4D21-80D7-E23EAC793ED9}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="8"/>
+          <c:order val="8"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet20!$A$10</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Polio</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Sheet20!$B$1:$K$1</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet20!$B$10:$K$10</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>609858544.70124209</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>731851945.02000213</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>625410897.66891646</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>802560866.6160953</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>838599026.6314044</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>700049356.03643107</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>728663200.72728252</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>759929687.82186258</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>919044045.79162061</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1098909029.1728315</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000008-1349-4D21-80D7-E23EAC793ED9}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="9"/>
+          <c:order val="9"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet20!$A$11</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>HPV</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Sheet20!$B$1:$K$1</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet20!$B$11:$K$11</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>25991935.038739532</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>32672389.333723851</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>35258738.193920977</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>40618137.224358499</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>60831495.681220591</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>49380766.019802466</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>75921028.526657015</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>57364080.2476006</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>79644848.508560121</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>97041798.950795934</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000009-1349-4D21-80D7-E23EAC793ED9}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="10"/>
+          <c:order val="10"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet20!$A$12</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Rotavirus</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent5">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Sheet20!$B$1:$K$1</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet20!$B$12:$K$12</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>213150623.17815194</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>136461943.51271439</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>285630581.28927135</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>90252569.704395846</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>521654929.0499537</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>281171491.36281955</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>714823089.07648277</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>570392658.13201773</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>434313063.99935478</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>866834289.19984269</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{0000000A-1349-4D21-80D7-E23EAC793ED9}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="11"/>
+          <c:order val="11"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet20!$A$13</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>PCV</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent6">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Sheet20!$B$1:$K$1</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet20!$B$13:$K$13</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>252940083.3603006</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>303936532.15251517</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>358050986.80952358</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>188469763.52293101</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>172308767.418744</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>381372721.84961098</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>450645114.26926851</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>415928904.92607629</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>519844013.69538343</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>453836107.44449335</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{0000000B-1349-4D21-80D7-E23EAC793ED9}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="1662209760"/>
+        <c:axId val="1662211200"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="1662209760"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1662211200"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1662211200"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1662209760"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet30!$A$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Measles</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Sheet30!$B$1:$K$1</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet30!$B$2:$K$2</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>352474390.72704268</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>810633988.61219323</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>447682416.90770262</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>257632543.94093996</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>134237518.08333459</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>596079100.54289305</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>98792333.830466211</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>481840574.93180472</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>497041658.45804787</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1152287601.6301403</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-30C8-4EC2-9581-53AF8F3E7223}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet30!$A$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Mumps</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Sheet30!$B$1:$K$1</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet30!$B$3:$K$3</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>15606210.17351607</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>47723828.221244819</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>46190011.777034625</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>33711309.215865165</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>29314807.734528963</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>41604291.288455196</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>39210946.803222828</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>64436042.557908103</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>47012392.291027322</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>63348981.055426799</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-30C8-4EC2-9581-53AF8F3E7223}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet30!$A$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Rubella</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Sheet30!$B$1:$K$1</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet30!$B$4:$K$4</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>444504796.73625731</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>656639443.69823086</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>475669117.50604105</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>331417291.27491212</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>393464689.43812037</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>893170870.4351871</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>202066492.85196459</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>241702879.81097811</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>997923120.84149313</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>703844043.92261708</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-30C8-4EC2-9581-53AF8F3E7223}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet30!$A$5</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Diphtheria</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Sheet30!$B$1:$K$1</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet30!$B$5:$K$5</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>777076702.64843607</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>902179583.3433063</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1048139752.510308</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>969136503.26083672</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1301197771.4069178</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1376904220.3253629</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>846880085.85955381</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1310820415.8623536</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1590088629.8728538</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1976154989.0500853</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-30C8-4EC2-9581-53AF8F3E7223}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="4"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet30!$A$6</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Tetanus</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent5"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Sheet30!$B$1:$K$1</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet30!$B$6:$K$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>670693824.74231339</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>714343852.26951778</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>712311918.63646388</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>625260629.79953015</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>553604179.03221846</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>853663027.37024045</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>589946267.37655365</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>832741679.05100286</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>552090282.89950347</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>761510099.97896969</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000004-30C8-4EC2-9581-53AF8F3E7223}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="5"/>
+          <c:order val="5"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet30!$A$7</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Pertussis</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent6"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Sheet30!$B$1:$K$1</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet30!$B$7:$K$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>397026393.63704878</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>329325023.90487802</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>284867436.90863109</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>354915877.22811699</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>306765879.12365264</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>338218288.21812248</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>331713757.70989567</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>289310691.67152917</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>452903244.45631611</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>359844430.78881615</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000005-30C8-4EC2-9581-53AF8F3E7223}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="6"/>
+          <c:order val="6"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet30!$A$8</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Hepatitis_B</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Sheet30!$B$1:$K$1</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet30!$B$8:$K$8</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>449867903.82097661</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>391226113.91316158</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>526172245.96548498</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>403280234.53635001</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>520206525.12671208</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>394452358.83252084</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>318533359.7639696</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>477030390.15036631</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>442839528.73916864</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>599483952.05527663</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000006-30C8-4EC2-9581-53AF8F3E7223}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="7"/>
+          <c:order val="7"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet30!$A$9</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Hib</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Sheet30!$B$1:$K$1</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet30!$B$9:$K$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>263149726.4973551</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>260202444.8283492</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>298702806.14663786</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>316571649.07319927</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>348495124.47789031</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>397185859.14710546</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>405632462.76411837</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>391031208.80974883</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>317415151.9805432</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>363065467.83188128</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000007-30C8-4EC2-9581-53AF8F3E7223}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="8"/>
+          <c:order val="8"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet30!$A$10</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Polio</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Sheet30!$B$1:$K$1</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet30!$B$10:$K$10</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>568135241.33461893</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>647996764.30085886</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>613612986.49106789</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>903868133.65732169</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>788967465.84432685</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>724971590.25218284</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>721950754.05530071</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>840581421.26758695</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>996677825.26266563</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>967580639.85507131</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000008-30C8-4EC2-9581-53AF8F3E7223}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="9"/>
+          <c:order val="9"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet30!$A$11</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>HPV</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Sheet30!$B$1:$K$1</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet30!$B$11:$K$11</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>25915770.51731832</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>32672389.333723851</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>46720358.840827107</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>39200401.038449273</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>48529207.558080085</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>63304158.954653658</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>65713275.787563398</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>71103149.090833336</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>77552496.90845111</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>85337783.57378386</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000009-30C8-4EC2-9581-53AF8F3E7223}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="10"/>
+          <c:order val="10"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet30!$A$12</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Rotavirus</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent5">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Sheet30!$B$1:$K$1</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet30!$B$12:$K$12</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>239577204.00124341</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>136461943.51271439</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>217203794.20830777</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>90252569.704395846</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>342127437.90788245</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>43127541.385232568</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>426273323.03115177</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>684578312.20058286</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1039102784.3477118</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>548432828.38315392</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{0000000A-30C8-4EC2-9581-53AF8F3E7223}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="11"/>
+          <c:order val="11"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet30!$A$13</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>PCV</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent6">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Sheet30!$B$1:$K$1</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet30!$B$13:$K$13</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>211403260.01881739</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>303936532.15251517</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>363423456.81929737</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>310232312.78781533</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>313516178.90166688</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>320814699.67499667</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>280679290.8361659</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>173579527.72382408</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>400984927.13776702</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>467549908.87879366</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{0000000B-30C8-4EC2-9581-53AF8F3E7223}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="1662208800"/>
+        <c:axId val="1662212160"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="1662208800"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1662212160"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1662212160"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1662208800"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>247650</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>42862</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>552450</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>119062</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{15168B61-6084-72B8-660F-D338B3BE32BD}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>209550</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>4762</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>514350</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>80962</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5AB5B59C-3D54-A67C-502F-9C785A93D6FF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>209550</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>109537</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>514350</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>185737</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0FED3C05-2114-1271-A44F-F2B1280B46BB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>23812</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>428625</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>100012</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2250D5BC-30DC-4FA5-2D5B-F128504D81D5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1403,6 +10171,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -3713,6 +12482,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -6495,6 +15265,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -11577,6 +20348,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
